--- a/data/trans_dic/P21D_1_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P21D_1_R-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria médica, no la pudo recibir por motivos económicos</t>
+          <t>Población que, necesitando atención sanitaria médica, no la pudo recibir por motivos económicos (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,65</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,24</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,17</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,1</t>
+          <t>0,0; 1,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,72</t>
+          <t>0,0; 0,55</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,77</t>
+          <t>0,0; 0,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,38</t>
+          <t>0,0; 0,4</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,17</t>
+          <t>0,0; 0,16</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria médica, no la pudo recibir por motivos económicos</t>
+          <t>Población que, necesitando atención sanitaria médica, no la pudo recibir por motivos económicos (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1735</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1111</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1340</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2960</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1217</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1876</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2016</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3633</t>
+          <t>0; 3537</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4743</t>
+          <t>0; 3611</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1834</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3983</t>
+          <t>0; 3288</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3522</t>
+          <t>0; 3674</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 2187</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4422</t>
+          <t>0; 4426</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 5380</t>
+          <t>0; 5358</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P21D_1_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P21D_1_R-Habitat-trans_dic.xlsx
@@ -654,12 +654,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,07</t>
+          <t>0,0; 1,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,55</t>
+          <t>0,0; 0,58</t>
         </is>
       </c>
     </row>
@@ -704,12 +704,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,63</t>
+          <t>0,0; 0,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,4</t>
+          <t>0,0; 0,38</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,28</t>
+          <t>0,0; 0,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1058,12 +1058,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>749</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>749</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3537</t>
+          <t>0; 3830</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3611</t>
+          <t>0; 4348</t>
         </is>
       </c>
     </row>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>702</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>702</t>
         </is>
       </c>
     </row>
@@ -1154,12 +1154,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3288</t>
+          <t>0; 3508</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3674</t>
+          <t>0; 3552</t>
         </is>
       </c>
     </row>
@@ -1204,12 +1204,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1451</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4426</t>
+          <t>0; 5349</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 5358</t>
+          <t>0; 5120</t>
         </is>
       </c>
     </row>
